--- a/data/credit_bond_all_2026-09-30.xlsx
+++ b/data/credit_bond_all_2026-09-30.xlsx
@@ -779,7 +779,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X3" s="3"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.68%</t>
+        </is>
+      </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -903,7 +907,9 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AZ3" s="3"/>
+      <c r="AZ3" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
@@ -995,7 +1001,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>1.46%~1.50%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1119,7 +1129,9 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1211,7 +1223,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X5" s="3"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>1.44%~1.48%</t>
+        </is>
+      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1335,7 +1351,9 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AZ5" s="3"/>
+      <c r="AZ5" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
@@ -1427,7 +1445,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>AA+</t>

--- a/data/credit_bond_all_2026-09-30.xlsx
+++ b/data/credit_bond_all_2026-09-30.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-30" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-01" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 44.31</t>
+          <t>B- 44.74</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -772,8 +772,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>2.8</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -971,7 +975,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C 29.36</t>
+          <t>C 29.03</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -994,7 +998,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>2.04</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
@@ -1208,7 +1214,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -1216,8 +1222,12 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -1430,7 +1440,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1439,7 +1449,9 @@
         </is>
       </c>
       <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+      <c r="V6" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
           <t>5-</t>

--- a/data/credit_bond_all_2026-09-30.xlsx
+++ b/data/credit_bond_all_2026-09-30.xlsx
@@ -700,7 +700,11 @@
           <t>09-30 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>012682371.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>0.73Y</t>
@@ -709,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>20.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.29 ~ 1.59</t>
@@ -926,7 +932,11 @@
           <t>09-30 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>012682370.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>0.39Y</t>
@@ -935,7 +945,9 @@
       <c r="E4" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.20 ~ 1.60</t>
@@ -1150,7 +1162,11 @@
           <t>09-30 18:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>012682369.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>0.12Y</t>
@@ -1159,7 +1175,9 @@
       <c r="E5" s="4" t="n">
         <v>3.0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.70</t>
@@ -1376,7 +1394,11 @@
           <t>09-30 18:00</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>102683861.IB</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -1385,7 +1407,9 @@
       <c r="E6" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 1.90</t>

--- a/data/credit_bond_all_2026-09-30.xlsx
+++ b/data/credit_bond_all_2026-09-30.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-01" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-02" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
     </row>

--- a/data/credit_bond_all_2026-09-30.xlsx
+++ b/data/credit_bond_all_2026-09-30.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-02" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-05" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
     </row>

--- a/data/credit_bond_all_2026-09-30.xlsx
+++ b/data/credit_bond_all_2026-09-30.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-05" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-06" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-05</t>
+          <t>数据来源：DM    2026-10-06</t>
         </is>
       </c>
     </row>
